--- a/sheet/Tier1_sheet.xlsx
+++ b/sheet/Tier1_sheet.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,46 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>crit_multiplier</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>armor_penetration</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>lifesteal</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>hp_regen</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>attack_variance_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" t="inlineStr">
@@ -551,6 +591,30 @@
       <c r="L2" t="n">
         <v>3</v>
       </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -589,6 +653,30 @@
       <c r="L3" t="n">
         <v>1</v>
       </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
@@ -627,6 +715,30 @@
       <c r="L4" t="n">
         <v>1</v>
       </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
@@ -665,6 +777,30 @@
       <c r="L5" t="n">
         <v>2</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -703,6 +839,30 @@
       <c r="L6" t="n">
         <v>1</v>
       </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -741,6 +901,30 @@
       <c r="L7" t="n">
         <v>1</v>
       </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -779,6 +963,30 @@
       <c r="L8" t="n">
         <v>1</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
@@ -817,6 +1025,30 @@
       <c r="L9" t="n">
         <v>1</v>
       </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="C10" t="inlineStr">
@@ -855,6 +1087,30 @@
       <c r="L10" t="n">
         <v>2</v>
       </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
@@ -893,6 +1149,30 @@
       <c r="L11" t="n">
         <v>1</v>
       </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
@@ -931,6 +1211,30 @@
       <c r="L12" t="n">
         <v>1</v>
       </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="C13" t="inlineStr">
@@ -969,6 +1273,30 @@
       <c r="L13" t="n">
         <v>3</v>
       </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="C14" t="inlineStr">
@@ -1007,6 +1335,30 @@
       <c r="L14" t="n">
         <v>2</v>
       </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
@@ -1045,6 +1397,30 @@
       <c r="L15" t="n">
         <v>2</v>
       </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
@@ -1083,6 +1459,30 @@
       <c r="L16" t="n">
         <v>1</v>
       </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
@@ -1121,6 +1521,30 @@
       <c r="L17" t="n">
         <v>3</v>
       </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="C18" t="inlineStr">
@@ -1159,6 +1583,30 @@
       <c r="L18" t="n">
         <v>2</v>
       </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
@@ -1197,6 +1645,30 @@
       <c r="L19" t="n">
         <v>1</v>
       </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
@@ -1235,6 +1707,30 @@
       <c r="L20" t="n">
         <v>2</v>
       </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -1273,6 +1769,30 @@
       <c r="L21" t="n">
         <v>1</v>
       </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
@@ -1311,6 +1831,30 @@
       <c r="L22" t="n">
         <v>3</v>
       </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="23">
       <c r="C23" t="inlineStr">
@@ -1349,6 +1893,30 @@
       <c r="L23" t="n">
         <v>2</v>
       </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="24">
       <c r="C24" t="inlineStr">
@@ -1387,6 +1955,30 @@
       <c r="L24" t="n">
         <v>2</v>
       </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
@@ -1424,6 +2016,30 @@
       </c>
       <c r="L25" t="n">
         <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1449,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1515,6 +2131,46 @@
           <t>range_bonus_pct</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>defense_bonus</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>crit_chance_bonus</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>crit_multiplier_bonus</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>armor_penetration_bonus</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>lifesteal_bonus</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>hp_regen_bonus</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>accuracy_bonus</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>attack_variance_pct_bonus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" t="inlineStr">
@@ -1541,6 +2197,30 @@
       <c r="H2" t="n">
         <v>0.1</v>
       </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -1567,6 +2247,30 @@
       <c r="H3" t="n">
         <v>0.12</v>
       </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
@@ -1593,6 +2297,30 @@
       <c r="H4" t="n">
         <v>0.14</v>
       </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
@@ -1619,6 +2347,30 @@
       <c r="H5" t="n">
         <v>0.16</v>
       </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -1645,6 +2397,30 @@
       <c r="H6" t="n">
         <v>0.1</v>
       </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -1671,6 +2447,30 @@
       <c r="H7" t="n">
         <v>0.11</v>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -1697,6 +2497,30 @@
       <c r="H8" t="n">
         <v>0.12</v>
       </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
@@ -1723,6 +2547,30 @@
       <c r="H9" t="n">
         <v>0.13</v>
       </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="C10" t="inlineStr">
@@ -1752,6 +2600,30 @@
       <c r="J10" t="n">
         <v>0.1</v>
       </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
@@ -1781,6 +2653,30 @@
       <c r="J11" t="n">
         <v>0.2</v>
       </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
@@ -1810,6 +2706,30 @@
       <c r="J12" t="n">
         <v>0.3</v>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="C13" t="inlineStr">
@@ -1839,6 +2759,30 @@
       <c r="J13" t="n">
         <v>0.2</v>
       </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="C14" t="inlineStr">
@@ -1868,6 +2812,30 @@
       <c r="J14" t="n">
         <v>0.3</v>
       </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
@@ -1897,6 +2865,30 @@
       <c r="J15" t="n">
         <v>0.4</v>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
@@ -1923,6 +2915,30 @@
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
@@ -1949,6 +2965,30 @@
       <c r="H17" t="n">
         <v>0.12</v>
       </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="C18" t="inlineStr">
@@ -1975,6 +3015,30 @@
       <c r="H18" t="n">
         <v>0.14</v>
       </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
@@ -2001,6 +3065,30 @@
       <c r="H19" t="n">
         <v>0.16</v>
       </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
@@ -2030,6 +3118,30 @@
       <c r="J20" t="n">
         <v>0.1</v>
       </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -2059,6 +3171,30 @@
       <c r="J21" t="n">
         <v>0.2</v>
       </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
@@ -2088,6 +3224,30 @@
       <c r="J22" t="n">
         <v>0.3</v>
       </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="C23" t="inlineStr">
@@ -2114,6 +3274,30 @@
       <c r="H23" t="n">
         <v>0.1</v>
       </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="C24" t="inlineStr">
@@ -2140,6 +3324,30 @@
       <c r="H24" t="n">
         <v>0.11</v>
       </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
@@ -2166,6 +3374,30 @@
       <c r="H25" t="n">
         <v>0.12</v>
       </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="C26" t="inlineStr">
@@ -2192,6 +3424,30 @@
       <c r="H26" t="n">
         <v>0.13</v>
       </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="C27" t="inlineStr">
@@ -2221,6 +3477,30 @@
       <c r="J27" t="n">
         <v>0.2</v>
       </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="C28" t="inlineStr">
@@ -2250,6 +3530,30 @@
       <c r="J28" t="n">
         <v>0.3</v>
       </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
@@ -2278,6 +3582,30 @@
       </c>
       <c r="J29" t="n">
         <v>0.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2291,7 +3619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2363,6 +3691,46 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>crit_multiplier</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>armor_penetration</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lifesteal</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>hp_regen</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>attack_variance_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2406,6 +3774,30 @@
           <t>기본 근접</t>
         </is>
       </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2449,6 +3841,30 @@
           <t>강화 근접</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2492,6 +3908,30 @@
           <t>원거리</t>
         </is>
       </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2535,6 +3975,30 @@
           <t>C1 산적 보스</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2578,6 +4042,30 @@
           <t>빠른 근접</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2621,6 +4109,30 @@
           <t>느린 탱커</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2663,6 +4175,30 @@
         <is>
           <t>C1 야수 보스</t>
         </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2676,7 +4212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2754,6 +4290,46 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>defense_bonus</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>crit_chance_bonus</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>crit_multiplier_bonus</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>armor_penetration_bonus</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>lifesteal_bonus</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>hp_regen_bonus</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>accuracy_bonus</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>attack_variance_pct_bonus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2802,6 +4378,30 @@
           <t>산적 3+ 시 전 산적 atk +30%</t>
         </is>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2850,6 +4450,30 @@
           <t>산적 5+ — Tier 치환 (horde 위 단계)</t>
         </is>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2898,6 +4522,30 @@
           <t>산적 두목 인접 부하 공속 +50%</t>
         </is>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2946,6 +4594,30 @@
           <t>야수 2+ 시 atk +10%, mvspd +25%</t>
         </is>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2994,6 +4666,30 @@
           <t>동료 사망 시 생존 산적 atk +10% (중첩, 상한 5)</t>
         </is>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3037,6 +4733,30 @@
           <t>자기 HP ≤40% 시 atk +30%, atkspd +20%</t>
         </is>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3079,6 +4799,30 @@
         <is>
           <t>적이 플레이어보다 2명+ 많으면 mvspd +25%</t>
         </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/Tier1_sheet.xlsx
+++ b/sheet/Tier1_sheet.xlsx
@@ -592,7 +592,7 @@
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.608</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -663,19 +663,19 @@
         <v>1.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P4" t="n">
         <v>1.5</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -778,10 +778,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="P5" t="n">
         <v>1.5</v>
@@ -796,10 +796,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
@@ -840,25 +840,25 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P6" t="n">
         <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="U6" t="n">
         <v>0.2</v>
@@ -902,10 +902,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P7" t="n">
         <v>1.5</v>
@@ -917,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="U7" t="n">
         <v>0.2</v>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -979,13 +979,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1035,19 +1035,19 @@
         <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -1088,10 +1088,10 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="P10" t="n">
         <v>1.5</v>
@@ -1103,13 +1103,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="11">
@@ -1150,13 +1150,13 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="U11" t="n">
         <v>0.2</v>
@@ -1215,22 +1215,22 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="U12" t="n">
         <v>0.2</v>
@@ -1277,10 +1277,10 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1289,13 +1289,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="14">
@@ -1336,13 +1336,13 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15">
@@ -1401,25 +1401,25 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16">
@@ -1463,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U16" t="n">
         <v>0.2</v>
@@ -1525,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="18">
@@ -1584,16 +1584,16 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="19">
@@ -1649,25 +1649,25 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="20">
@@ -1708,28 +1708,28 @@
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="P20" t="n">
         <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21">
@@ -1770,25 +1770,25 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P21" t="n">
         <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U21" t="n">
         <v>0.2</v>
@@ -1832,28 +1832,28 @@
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="P22" t="n">
         <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23">
@@ -1897,16 +1897,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="24">
@@ -1956,28 +1956,28 @@
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="25">
@@ -2021,25 +2021,25 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -3775,25 +3775,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N2" t="n">
         <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S2" t="n">
         <v>0.2</v>
@@ -3842,25 +3842,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N3" t="n">
         <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S3" t="n">
         <v>0.2</v>
@@ -3909,25 +3909,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N4" t="n">
         <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S4" t="n">
         <v>0.2</v>
@@ -3976,25 +3976,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="S5" t="n">
         <v>0.2</v>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -4125,13 +4125,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -4177,28 +4177,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/Tier1_sheet.xlsx
+++ b/sheet/Tier1_sheet.xlsx
@@ -14,7 +14,7 @@
     <sheet name="encounters_slots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -555,6 +555,16 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ven_infantry_soldier</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>터커</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>벤</t>
@@ -617,6 +627,16 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ven_infantry_mercenary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>크리스</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>벤</t>
@@ -679,6 +699,16 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ven_infantry_adventurer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>존</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>벤</t>
@@ -741,6 +771,16 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ven_spearman_soldier</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>해리스</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>벤</t>
@@ -803,6 +843,16 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ven_spearman_mercenary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>케인</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>벤</t>
@@ -865,6 +915,16 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ven_spearman_adventurer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>브렌</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>벤</t>
@@ -927,6 +987,16 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>krem_infantry_soldier</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>할리</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>크렘</t>
@@ -989,6 +1059,16 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>krem_infantry_mercenary</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>알렉스</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>크렘</t>
@@ -1051,6 +1131,16 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>krem_infantry_adventurer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>스미스</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>크렘</t>
@@ -1113,6 +1203,16 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>krem_archer_soldier</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>에이든</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>크렘</t>
@@ -1175,6 +1275,16 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>krem_archer_mercenary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>세르다스</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>크렘</t>
@@ -1237,6 +1347,16 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>krem_archer_adventurer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>데미안</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>크렘</t>
@@ -1299,6 +1419,16 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>arden_archer_soldier</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>제인</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>아르덴</t>
@@ -1361,6 +1491,16 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>arden_archer_mercenary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>메이드</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>아르덴</t>
@@ -1423,6 +1563,16 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>arden_archer_adventurer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>센크리드</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>아르덴</t>
@@ -1485,6 +1635,16 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>arden_crossbowman_mercenary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>팜</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>아르덴</t>
@@ -1547,6 +1707,16 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>arden_crossbowman_soldier</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>트리니티</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>아르덴</t>
@@ -1609,6 +1779,16 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>arden_crossbowman_adventurer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>레너드</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>아르덴</t>
@@ -1671,6 +1851,16 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>nelm_spearman_soldier</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>블라드</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>넬름</t>
@@ -1733,6 +1923,16 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>nelm_spearman_mercenary</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>세이지</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>넬름</t>
@@ -1795,6 +1995,16 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nelm_spearman_adventurer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>헤럴드</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>넬름</t>
@@ -1857,6 +2067,16 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>nelm_crossbowman_mercenary</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>르만다</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>넬름</t>
@@ -1919,6 +2139,16 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>nelm_crossbowman_soldier</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>개리</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>넬름</t>
@@ -1981,6 +2211,16 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>nelm_crossbowman_adventurer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>운타라</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>넬름</t>
@@ -2069,7 +2309,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="32.5" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="14.875" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="21.75" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -2078,6 +2318,14 @@
     <col width="13.5" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="23" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="16.375" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="14.625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="17.625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="20" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="24.5" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="14.375" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="16" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="15.25" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="25.25" bestFit="1" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2173,6 +2421,16 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>syn_ven_infantry_t2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>벤 보병단(2)</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>벤 보병이 인접했을 때 발동</t>
@@ -2223,6 +2481,16 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>syn_ven_infantry_t3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>벤 보병단(3)</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>벤 보병이 인접했을 때 발동</t>
@@ -2273,6 +2541,16 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>syn_ven_infantry_t4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>벤 보병단(4)</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>벤 보병이 인접했을 때 발동</t>
@@ -2323,6 +2601,16 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>syn_ven_infantry_t5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>벤 보병단(5)</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>벤 보병이 인접했을 때 발동</t>
@@ -2373,6 +2661,16 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>syn_ven_spearman_t2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>벤 창병단(2)</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>벤 창병이 인접했을 때 발동</t>
@@ -2423,6 +2721,16 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>syn_ven_spearman_t3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>벤 창병단(3)</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>벤 창병이 인접했을 때 발동</t>
@@ -2473,6 +2781,16 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>syn_ven_spearman_t4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>벤 창병단(4)</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>벤 창병이 인접했을 때 발동</t>
@@ -2523,6 +2841,16 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>syn_ven_spearman_t5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>벤 창병단(5)</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>벤 창병이 인접했을 때 발동</t>
@@ -2573,6 +2901,16 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>syn_arden_archer_t2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>아르덴 궁수대(2)</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>아르덴 궁병이 인접했을 때 발동</t>
@@ -2626,6 +2964,16 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>syn_arden_archer_t3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>아르덴 궁수대(3)</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>아르덴 궁병이 인접했을 때 발동</t>
@@ -2679,6 +3027,16 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>syn_arden_archer_t4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>아르덴 궁수대(4)</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>아르덴 궁병이 인접했을 때 발동</t>
@@ -2732,6 +3090,16 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>syn_arden_crossbowman_t2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>아르덴 석궁대(2)</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>아르덴 석궁병이 인접했을 때 발동</t>
@@ -2785,6 +3153,16 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>syn_arden_crossbowman_t3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>아르덴 석궁대(3)</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>아르덴 석궁병이 인접했을 때 발동</t>
@@ -2838,6 +3216,16 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>syn_arden_crossbowman_t4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>아르덴 석궁대(4)</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>아르덴 석궁병이 인접했을 때 발동</t>
@@ -2891,6 +3279,16 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>syn_krem_infantry_t2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>크렘 철벽 보병단(2)</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>크렘 보병이 인접했을 때 발동</t>
@@ -2941,6 +3339,16 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>syn_krem_infantry_t3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>크렘 철벽 보병단(3)</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>크렘 보병이 인접했을 때 발동</t>
@@ -2991,6 +3399,16 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>syn_krem_infantry_t4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>크렘 철벽 보병단(4)</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>크렘 보병이 인접했을 때 발동</t>
@@ -3041,6 +3459,16 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syn_krem_infantry_t5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>크렘 철벽 보병단(5)</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>크렘 보병이 인접했을 때 발동</t>
@@ -3091,6 +3519,16 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syn_krem_archer_t2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>크렘 사수대(2)</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>크렘 궁병이 인접했을 때 발동</t>
@@ -3144,6 +3582,16 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>syn_krem_archer_t3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>크렘 사수대(3)</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>크렘 궁병이 인접했을 때 발동</t>
@@ -3197,6 +3645,16 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>syn_krem_archer_t4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>크렘 사수대(4)</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>크렘 궁병이 인접했을 때 발동</t>
@@ -3250,6 +3708,16 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>syn_nelm_spearman_t2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>넬름 장창 방진(2)</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>넬름 창병이 인접했을 때 발동</t>
@@ -3300,6 +3768,16 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>syn_nelm_spearman_t3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>넬름 장창 방진(3)</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>넬름 창병이 인접했을 때 발동</t>
@@ -3350,6 +3828,16 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>syn_nelm_spearman_t4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>넬름 장창 방진(4)</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>넬름 창병이 인접했을 때 발동</t>
@@ -3400,6 +3888,16 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>syn_nelm_spearman_t5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>넬름 장창 방진(5)</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>넬름 창병이 인접했을 때 발동</t>
@@ -3450,6 +3948,16 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>syn_nelm_crossbowman_t2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>넬름 석궁대(2)</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>넬름 석궁병이 인접했을 때 발동</t>
@@ -3503,6 +4011,16 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>syn_nelm_crossbowman_t3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>넬름 석궁대(3)</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>넬름 석궁병이 인접했을 때 발동</t>
@@ -3556,6 +4074,16 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>syn_nelm_crossbowman_t4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>넬름 석궁대(4)</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>넬름 석궁병이 인접했을 때 발동</t>
@@ -3622,8 +4150,8 @@
   <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.75" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="8" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="6.625" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="12.625" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -3632,7 +4160,15 @@
     <col width="11.75" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="7.25" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="4.25" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="6.125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="12.75" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="8.125" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="11" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="13.375" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="17.875" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="8" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="9.375" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="8.75" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="18.625" bestFit="1" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4839,13 +5375,12 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="3.125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="7.75" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="5.25" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="3" max="4"/>
     <col width="21.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="7.875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="6.125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="61.75" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="35.375" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
